--- a/experiment/Omni+CNN_2CH_bestx4/Test/results-Set14/Set14.xlsx
+++ b/experiment/Omni+CNN_2CH_bestx4/Test/results-Set14/Set14.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23.02</v>
+        <v>23.04</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5344</v>
+        <v>0.5365</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.04</v>
+        <v>26.06</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7544</v>
+        <v>0.7554</v>
       </c>
     </row>
     <row r="4">
@@ -481,7 +481,7 @@
         <v>25.41</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6377</v>
+        <v>0.6383</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.26</v>
+        <v>26.31</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5784</v>
+        <v>0.5793</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>23.62</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7397</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.89</v>
+        <v>32.92</v>
       </c>
       <c r="C7" t="n">
-        <v>0.795</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.36</v>
+        <v>28.38</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8219</v>
+        <v>0.8231000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.95</v>
+        <v>33.77</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9224</v>
+        <v>0.9203</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32.48</v>
+        <v>32.52</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8648</v>
+        <v>0.8653999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.4</v>
+        <v>27.39</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7509</v>
+        <v>0.7514999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32.91</v>
+        <v>33.03</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9459</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>34.31</v>
+        <v>34.29</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8804999999999999</v>
+        <v>0.8802</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26.68</v>
+        <v>26.71</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9492</v>
+        <v>0.9497</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.42</v>
+        <v>27.32</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7793</v>
+        <v>0.7781</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28.62</v>
+        <v>28.63</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7824</v>
+        <v>0.7828000000000001</v>
       </c>
     </row>
   </sheetData>
